--- a/content/multivariate_statistics/data/pine_needles.xlsx
+++ b/content/multivariate_statistics/data/pine_needles.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wlperry/Desktop/www_umd_biostats/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C755C988-DBAE-9D4D-9FCA-F85E0F68617A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="50040" yWindow="-1220" windowWidth="28100" windowHeight="17440" xr2:uid="{4D25EE0D-EF4D-8046-90A6-109745D58C50}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="14">
   <si>
     <t>date</t>
   </si>
@@ -44,25 +22,31 @@
     <t>group</t>
   </si>
   <si>
-    <t>cephalopods</t>
+    <t>n_s</t>
   </si>
   <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>n_s</t>
+    <t>sun</t>
   </si>
   <si>
     <t>tree_no</t>
   </si>
   <si>
+    <t>length_mm</t>
+  </si>
+  <si>
+    <t>cephalopods</t>
+  </si>
+  <si>
     <t>n</t>
   </si>
   <si>
-    <t>lee</t>
+    <t>shady</t>
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>sunny</t>
   </si>
   <si>
     <t>salmon</t>
@@ -73,20 +57,29 @@
   <si>
     <t>snail</t>
   </si>
-  <si>
-    <t>length_mm</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="ArialMT"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,23 +102,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -140,44 +128,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -204,32 +192,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -256,24 +226,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -285,188 +237,195 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A220954B-A562-7C48-AB0D-991C41FC0941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -474,13 +433,13 @@
         <v>45736</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -494,13 +453,13 @@
         <v>45736</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -514,13 +473,13 @@
         <v>45736</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -534,13 +493,13 @@
         <v>45736</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -554,13 +513,13 @@
         <v>45736</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -574,13 +533,13 @@
         <v>45736</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -594,13 +553,13 @@
         <v>45736</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -614,13 +573,13 @@
         <v>45736</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -634,13 +593,13 @@
         <v>45736</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -654,13 +613,13 @@
         <v>45736</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -674,13 +633,13 @@
         <v>45736</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -694,13 +653,13 @@
         <v>45736</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -714,13 +673,13 @@
         <v>45736</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -734,13 +693,13 @@
         <v>45736</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -754,13 +713,13 @@
         <v>45736</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -774,13 +733,13 @@
         <v>45736</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -794,13 +753,13 @@
         <v>45736</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -814,13 +773,13 @@
         <v>45736</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -834,13 +793,13 @@
         <v>45736</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -854,13 +813,13 @@
         <v>45736</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -874,13 +833,13 @@
         <v>45736</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -894,13 +853,13 @@
         <v>45736</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -914,13 +873,13 @@
         <v>45736</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -934,13 +893,13 @@
         <v>45736</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -954,13 +913,13 @@
         <v>45736</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -974,13 +933,13 @@
         <v>45736</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -994,13 +953,13 @@
         <v>45736</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -1014,13 +973,13 @@
         <v>45736</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1034,13 +993,13 @@
         <v>45736</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -1054,13 +1013,13 @@
         <v>45736</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -1074,13 +1033,13 @@
         <v>45736</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -1094,13 +1053,13 @@
         <v>45736</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -1114,13 +1073,13 @@
         <v>45736</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -1134,13 +1093,13 @@
         <v>45736</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1154,13 +1113,13 @@
         <v>45736</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -1174,13 +1133,13 @@
         <v>45736</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -1194,13 +1153,13 @@
         <v>45736</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>4</v>
@@ -1214,13 +1173,13 @@
         <v>45736</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -1234,13 +1193,13 @@
         <v>45736</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40">
         <v>4</v>
@@ -1254,13 +1213,13 @@
         <v>45736</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -1274,13 +1233,13 @@
         <v>45736</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -1294,13 +1253,13 @@
         <v>45736</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>4</v>
@@ -1314,13 +1273,13 @@
         <v>45736</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E44">
         <v>4</v>
@@ -1334,13 +1293,13 @@
         <v>45736</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>4</v>
@@ -1354,13 +1313,13 @@
         <v>45736</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -1374,13 +1333,13 @@
         <v>45736</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>4</v>
@@ -1394,13 +1353,13 @@
         <v>45736</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -1414,13 +1373,13 @@
         <v>45736</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49">
         <v>4</v>
